--- a/TEXTRADE/TEXTRADE/DOCUMENTATION/MASHOKKUMAR/RS.xlsx
+++ b/TEXTRADE/TEXTRADE/DOCUMENTATION/MASHOKKUMAR/RS.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NEWSERVER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\TEXTRADE\TEXTRADE\TEXTRADE\DOCUMENTATION\MASHOKKUMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3119A3E1-DD21-4B3D-BBC6-3ABE20C901C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{D80741B9-B7C2-4BEC-AF8A-9FF1A201FAA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="job work bills to be uploaded" sheetId="1" r:id="rId1"/>
@@ -202,7 +201,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -548,7 +547,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C707A1D-05BC-4AC2-ADDE-DB7246D67989}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -788,7 +787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9DD102-EC9F-4A40-9503-AE3C8DA682BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
